--- a/backend/templates/base/base_proctor.xlsx
+++ b/backend/templates/base/base_proctor.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="CurvaX">'_DATOS'!$A$3:$A$6</definedName>
     <definedName name="CurvaY">'_DATOS'!$B$3:$B$6</definedName>
-    <definedName name="AjusteX">'_DATOS'!$H$3:$H$22</definedName>
-    <definedName name="AjusteY">'_DATOS'!$I$3:$I$22</definedName>
+    <definedName name="AjusteX">'_DATOS'!$H$3:$H$203</definedName>
+    <definedName name="AjusteY">'_DATOS'!$I$3:$I$203</definedName>
     <definedName name="MDSX">'_DATOS'!$K$3</definedName>
     <definedName name="MDSY">'_DATOS'!$L$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Reporte'!$A$1:$I$78</definedName>
@@ -415,7 +415,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Ajuste Cuadrático</v>
+            <v>Ajuste MTC (Cúbico)</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
@@ -435,12 +435,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'_DATOS'!$H$3:$H$22</f>
+              <f>'_DATOS'!$H$3:$H$203</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'_DATOS'!$I$3:$I$22</f>
+              <f>'_DATOS'!$I$3:$I$203</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -1772,18 +1772,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="F1">
-        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2}),1,1),"")</f>
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2,3}),1,1),"")</f>
+        <v/>
+      </c>
+      <c r="G1">
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2,3}),1,4),"")</f>
         <v/>
       </c>
     </row>
     <row r="2">
       <c r="F2">
-        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2}),1,2),"")</f>
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2,3}),1,2),"")</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>IF(COUNT(A3:A6)&lt;4,NA(),MIN(A3:A6)-0.05*(MAX(A3:A6)-MIN(A3:A6)))</f>
         <v/>
       </c>
     </row>
@@ -1797,15 +1805,19 @@
         <v/>
       </c>
       <c r="F3">
-        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2}),1,3),"")</f>
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2,3}),1,3),"")</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF(NOT(ISNUMBER(G2)),NA(),((MAX(A3:A6)+0.05*(MAX(A3:A6)-MIN(A3:A6)))-G2)/200)</f>
         <v/>
       </c>
       <c r="H3">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>IF(ISNA(H3),NA(),$F$1*H3^2+$F$2*H3+$F$3)</f>
+        <f>IF(H3="","",$F$1*H3^3+$F$2*H3^2+$F$3*H3+$G$1)</f>
         <v/>
       </c>
       <c r="K3">
@@ -1827,15 +1839,15 @@
         <v/>
       </c>
       <c r="F4">
-        <f>IF(AND(ISNUMBER(F1),N(F1)&lt;&gt;0),-F2/(2*F1),"")</f>
+        <f>IF(COUNT($A$3:$A$6)&gt;=4,IFERROR(INDEX($H$3:$H$203,MATCH(MAX($I$3:$I$203),$I$3:$I$203,0)),""),IF(ISNUMBER($F$11),$F$11,""))</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(ISNA(H4),NA(),$F$1*H4^2+$F$2*H4+$F$3)</f>
+        <f>IF(H4="","",$F$1*H4^3+$F$2*H4^2+$F$3*H4+$G$1)</f>
         <v/>
       </c>
     </row>
@@ -1849,15 +1861,15 @@
         <v/>
       </c>
       <c r="F5">
-        <f>IF(ISNUMBER(F4),F1*F4^2+F2*F4+F3,"")</f>
+        <f>IF(COUNT($A$3:$A$6)&gt;=4,IFERROR(MAX($I$3:$I$203),""),IF(ISNUMBER($F$12),$F$12,""))</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(ISNA(H5),NA(),$F$1*H5^2+$F$2*H5+$F$3)</f>
+        <f>IF(H5="","",$F$1*H5^3+$F$2*H5^2+$F$3*H5+$G$1)</f>
         <v/>
       </c>
     </row>
@@ -1871,171 +1883,2001 @@
         <v/>
       </c>
       <c r="H6">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IF(ISNA(H6),NA(),$F$1*H6^2+$F$2*H6+$F$3)</f>
+        <f>IF(H6="","",$F$1*H6^3+$F$2*H6^2+$F$3*H6+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="H7">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I7">
-        <f>IF(ISNA(H7),NA(),$F$1*H7^2+$F$2*H7+$F$3)</f>
+        <f>IF(H7="","",$F$1*H7^3+$F$2*H7^2+$F$3*H7+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="8">
+      <c r="F8">
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2}),1,1),"")</f>
+        <v/>
+      </c>
       <c r="H8">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(ISNA(H8),NA(),$F$1*H8^2+$F$2*H8+$F$3)</f>
+        <f>IF(H8="","",$F$1*H8^3+$F$2*H8^2+$F$3*H8+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="9">
+      <c r="F9">
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2}),1,2),"")</f>
+        <v/>
+      </c>
       <c r="H9">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(ISNA(H9),NA(),$F$1*H9^2+$F$2*H9+$F$3)</f>
+        <f>IF(H9="","",$F$1*H9^3+$F$2*H9^2+$F$3*H9+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="10">
+      <c r="F10">
+        <f>IFERROR(INDEX(LINEST(B3:B6,A3:A6^{1,2}),1,3),"")</f>
+        <v/>
+      </c>
       <c r="H10">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I10">
-        <f>IF(ISNA(H10),NA(),$F$1*H10^2+$F$2*H10+$F$3)</f>
+        <f>IF(H10="","",$F$1*H10^3+$F$2*H10^2+$F$3*H10+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="11">
+      <c r="F11">
+        <f>IF(AND(ISNUMBER(F8),N(F8)&lt;&gt;0),-F9/(2*F8),"")</f>
+        <v/>
+      </c>
       <c r="H11">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I11">
-        <f>IF(ISNA(H11),NA(),$F$1*H11^2+$F$2*H11+$F$3)</f>
+        <f>IF(H11="","",$F$1*H11^3+$F$2*H11^2+$F$3*H11+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="12">
+      <c r="F12">
+        <f>IF(ISNUMBER(F11),F8*F11^2+F9*F11+F10,"")</f>
+        <v/>
+      </c>
       <c r="H12">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(ISNA(H12),NA(),$F$1*H12^2+$F$2*H12+$F$3)</f>
+        <f>IF(H12="","",$F$1*H12^3+$F$2*H12^2+$F$3*H12+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="H13">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(ISNA(H13),NA(),$F$1*H13^2+$F$2*H13+$F$3)</f>
+        <f>IF(H13="","",$F$1*H13^3+$F$2*H13^2+$F$3*H13+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="H14">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I14">
-        <f>IF(ISNA(H14),NA(),$F$1*H14^2+$F$2*H14+$F$3)</f>
+        <f>IF(H14="","",$F$1*H14^3+$F$2*H14^2+$F$3*H14+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="H15">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I15">
-        <f>IF(ISNA(H15),NA(),$F$1*H15^2+$F$2*H15+$F$3)</f>
+        <f>IF(H15="","",$F$1*H15^3+$F$2*H15^2+$F$3*H15+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="H16">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I16">
-        <f>IF(ISNA(H16),NA(),$F$1*H16^2+$F$2*H16+$F$3)</f>
+        <f>IF(H16="","",$F$1*H16^3+$F$2*H16^2+$F$3*H16+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="H17">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I17">
-        <f>IF(ISNA(H17),NA(),$F$1*H17^2+$F$2*H17+$F$3)</f>
+        <f>IF(H17="","",$F$1*H17^3+$F$2*H17^2+$F$3*H17+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="H18">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I18">
-        <f>IF(ISNA(H18),NA(),$F$1*H18^2+$F$2*H18+$F$3)</f>
+        <f>IF(H18="","",$F$1*H18^3+$F$2*H18^2+$F$3*H18+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="H19">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I19">
-        <f>IF(ISNA(H19),NA(),$F$1*H19^2+$F$2*H19+$F$3)</f>
+        <f>IF(H19="","",$F$1*H19^3+$F$2*H19^2+$F$3*H19+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="H20">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>IF(ISNA(H20),NA(),$F$1*H20^2+$F$2*H20+$F$3)</f>
+        <f>IF(H20="","",$F$1*H20^3+$F$2*H20^2+$F$3*H20+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="H21">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I21">
-        <f>IF(ISNA(H21),NA(),$F$1*H21^2+$F$2*H21+$F$3)</f>
+        <f>IF(H21="","",$F$1*H21^3+$F$2*H21^2+$F$3*H21+$G$1)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="H22">
-        <f>IF(OR(NOT(ISNUMBER($F$1)),NOT(ISNUMBER($F$4))),NA(),$F$4+(ROW()-13)*0.5)</f>
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
         <v/>
       </c>
       <c r="I22">
-        <f>IF(ISNA(H22),NA(),$F$1*H22^2+$F$2*H22+$F$3)</f>
+        <f>IF(H22="","",$F$1*H22^3+$F$2*H22^2+$F$3*H22+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",$F$1*H23^3+$F$2*H23^2+$F$3*H23+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",$F$1*H24^3+$F$2*H24^2+$F$3*H24+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",$F$1*H25^3+$F$2*H25^2+$F$3*H25+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",$F$1*H26^3+$F$2*H26^2+$F$3*H26+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",$F$1*H27^3+$F$2*H27^2+$F$3*H27+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",$F$1*H28^3+$F$2*H28^2+$F$3*H28+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",$F$1*H29^3+$F$2*H29^2+$F$3*H29+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",$F$1*H30^3+$F$2*H30^2+$F$3*H30+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>IF(H31="","",$F$1*H31^3+$F$2*H31^2+$F$3*H31+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>IF(H32="","",$F$1*H32^3+$F$2*H32^2+$F$3*H32+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>IF(H33="","",$F$1*H33^3+$F$2*H33^2+$F$3*H33+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>IF(H34="","",$F$1*H34^3+$F$2*H34^2+$F$3*H34+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>IF(H35="","",$F$1*H35^3+$F$2*H35^2+$F$3*H35+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I36">
+        <f>IF(H36="","",$F$1*H36^3+$F$2*H36^2+$F$3*H36+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>IF(H37="","",$F$1*H37^3+$F$2*H37^2+$F$3*H37+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>IF(H38="","",$F$1*H38^3+$F$2*H38^2+$F$3*H38+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>IF(H39="","",$F$1*H39^3+$F$2*H39^2+$F$3*H39+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>IF(H40="","",$F$1*H40^3+$F$2*H40^2+$F$3*H40+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I41">
+        <f>IF(H41="","",$F$1*H41^3+$F$2*H41^2+$F$3*H41+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I42">
+        <f>IF(H42="","",$F$1*H42^3+$F$2*H42^2+$F$3*H42+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I43">
+        <f>IF(H43="","",$F$1*H43^3+$F$2*H43^2+$F$3*H43+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I44">
+        <f>IF(H44="","",$F$1*H44^3+$F$2*H44^2+$F$3*H44+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I45">
+        <f>IF(H45="","",$F$1*H45^3+$F$2*H45^2+$F$3*H45+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I46">
+        <f>IF(H46="","",$F$1*H46^3+$F$2*H46^2+$F$3*H46+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I47">
+        <f>IF(H47="","",$F$1*H47^3+$F$2*H47^2+$F$3*H47+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I48">
+        <f>IF(H48="","",$F$1*H48^3+$F$2*H48^2+$F$3*H48+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I49">
+        <f>IF(H49="","",$F$1*H49^3+$F$2*H49^2+$F$3*H49+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I50">
+        <f>IF(H50="","",$F$1*H50^3+$F$2*H50^2+$F$3*H50+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I51">
+        <f>IF(H51="","",$F$1*H51^3+$F$2*H51^2+$F$3*H51+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I52">
+        <f>IF(H52="","",$F$1*H52^3+$F$2*H52^2+$F$3*H52+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I53">
+        <f>IF(H53="","",$F$1*H53^3+$F$2*H53^2+$F$3*H53+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I54">
+        <f>IF(H54="","",$F$1*H54^3+$F$2*H54^2+$F$3*H54+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I55">
+        <f>IF(H55="","",$F$1*H55^3+$F$2*H55^2+$F$3*H55+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I56">
+        <f>IF(H56="","",$F$1*H56^3+$F$2*H56^2+$F$3*H56+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="H57">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I57">
+        <f>IF(H57="","",$F$1*H57^3+$F$2*H57^2+$F$3*H57+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="H58">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I58">
+        <f>IF(H58="","",$F$1*H58^3+$F$2*H58^2+$F$3*H58+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I59">
+        <f>IF(H59="","",$F$1*H59^3+$F$2*H59^2+$F$3*H59+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="H60">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I60">
+        <f>IF(H60="","",$F$1*H60^3+$F$2*H60^2+$F$3*H60+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I61">
+        <f>IF(H61="","",$F$1*H61^3+$F$2*H61^2+$F$3*H61+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I62">
+        <f>IF(H62="","",$F$1*H62^3+$F$2*H62^2+$F$3*H62+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="H63">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I63">
+        <f>IF(H63="","",$F$1*H63^3+$F$2*H63^2+$F$3*H63+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="H64">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I64">
+        <f>IF(H64="","",$F$1*H64^3+$F$2*H64^2+$F$3*H64+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I65">
+        <f>IF(H65="","",$F$1*H65^3+$F$2*H65^2+$F$3*H65+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I66">
+        <f>IF(H66="","",$F$1*H66^3+$F$2*H66^2+$F$3*H66+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I67">
+        <f>IF(H67="","",$F$1*H67^3+$F$2*H67^2+$F$3*H67+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I68">
+        <f>IF(H68="","",$F$1*H68^3+$F$2*H68^2+$F$3*H68+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I69">
+        <f>IF(H69="","",$F$1*H69^3+$F$2*H69^2+$F$3*H69+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I70">
+        <f>IF(H70="","",$F$1*H70^3+$F$2*H70^2+$F$3*H70+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="H71">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I71">
+        <f>IF(H71="","",$F$1*H71^3+$F$2*H71^2+$F$3*H71+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I72">
+        <f>IF(H72="","",$F$1*H72^3+$F$2*H72^2+$F$3*H72+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>IF(H73="","",$F$1*H73^3+$F$2*H73^2+$F$3*H73+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I74">
+        <f>IF(H74="","",$F$1*H74^3+$F$2*H74^2+$F$3*H74+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="H75">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I75">
+        <f>IF(H75="","",$F$1*H75^3+$F$2*H75^2+$F$3*H75+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="H76">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>IF(H76="","",$F$1*H76^3+$F$2*H76^2+$F$3*H76+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="H77">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>IF(H77="","",$F$1*H77^3+$F$2*H77^2+$F$3*H77+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="H78">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>IF(H78="","",$F$1*H78^3+$F$2*H78^2+$F$3*H78+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I79">
+        <f>IF(H79="","",$F$1*H79^3+$F$2*H79^2+$F$3*H79+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>IF(H80="","",$F$1*H80^3+$F$2*H80^2+$F$3*H80+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I81">
+        <f>IF(H81="","",$F$1*H81^3+$F$2*H81^2+$F$3*H81+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="H82">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I82">
+        <f>IF(H82="","",$F$1*H82^3+$F$2*H82^2+$F$3*H82+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="H83">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I83">
+        <f>IF(H83="","",$F$1*H83^3+$F$2*H83^2+$F$3*H83+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I84">
+        <f>IF(H84="","",$F$1*H84^3+$F$2*H84^2+$F$3*H84+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="H85">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>IF(H85="","",$F$1*H85^3+$F$2*H85^2+$F$3*H85+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="H86">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I86">
+        <f>IF(H86="","",$F$1*H86^3+$F$2*H86^2+$F$3*H86+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I87">
+        <f>IF(H87="","",$F$1*H87^3+$F$2*H87^2+$F$3*H87+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="H88">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I88">
+        <f>IF(H88="","",$F$1*H88^3+$F$2*H88^2+$F$3*H88+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="H89">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I89">
+        <f>IF(H89="","",$F$1*H89^3+$F$2*H89^2+$F$3*H89+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="H90">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I90">
+        <f>IF(H90="","",$F$1*H90^3+$F$2*H90^2+$F$3*H90+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="H91">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I91">
+        <f>IF(H91="","",$F$1*H91^3+$F$2*H91^2+$F$3*H91+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="H92">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I92">
+        <f>IF(H92="","",$F$1*H92^3+$F$2*H92^2+$F$3*H92+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="H93">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I93">
+        <f>IF(H93="","",$F$1*H93^3+$F$2*H93^2+$F$3*H93+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="H94">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I94">
+        <f>IF(H94="","",$F$1*H94^3+$F$2*H94^2+$F$3*H94+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="H95">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I95">
+        <f>IF(H95="","",$F$1*H95^3+$F$2*H95^2+$F$3*H95+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="H96">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I96">
+        <f>IF(H96="","",$F$1*H96^3+$F$2*H96^2+$F$3*H96+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="H97">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I97">
+        <f>IF(H97="","",$F$1*H97^3+$F$2*H97^2+$F$3*H97+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="H98">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I98">
+        <f>IF(H98="","",$F$1*H98^3+$F$2*H98^2+$F$3*H98+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="H99">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I99">
+        <f>IF(H99="","",$F$1*H99^3+$F$2*H99^2+$F$3*H99+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="H100">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I100">
+        <f>IF(H100="","",$F$1*H100^3+$F$2*H100^2+$F$3*H100+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="H101">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I101">
+        <f>IF(H101="","",$F$1*H101^3+$F$2*H101^2+$F$3*H101+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="H102">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I102">
+        <f>IF(H102="","",$F$1*H102^3+$F$2*H102^2+$F$3*H102+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I103">
+        <f>IF(H103="","",$F$1*H103^3+$F$2*H103^2+$F$3*H103+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I104">
+        <f>IF(H104="","",$F$1*H104^3+$F$2*H104^2+$F$3*H104+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I105">
+        <f>IF(H105="","",$F$1*H105^3+$F$2*H105^2+$F$3*H105+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I106">
+        <f>IF(H106="","",$F$1*H106^3+$F$2*H106^2+$F$3*H106+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I107">
+        <f>IF(H107="","",$F$1*H107^3+$F$2*H107^2+$F$3*H107+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="H108">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I108">
+        <f>IF(H108="","",$F$1*H108^3+$F$2*H108^2+$F$3*H108+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="H109">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I109">
+        <f>IF(H109="","",$F$1*H109^3+$F$2*H109^2+$F$3*H109+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="H110">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I110">
+        <f>IF(H110="","",$F$1*H110^3+$F$2*H110^2+$F$3*H110+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="H111">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I111">
+        <f>IF(H111="","",$F$1*H111^3+$F$2*H111^2+$F$3*H111+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="H112">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I112">
+        <f>IF(H112="","",$F$1*H112^3+$F$2*H112^2+$F$3*H112+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="H113">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I113">
+        <f>IF(H113="","",$F$1*H113^3+$F$2*H113^2+$F$3*H113+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="H114">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I114">
+        <f>IF(H114="","",$F$1*H114^3+$F$2*H114^2+$F$3*H114+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="H115">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I115">
+        <f>IF(H115="","",$F$1*H115^3+$F$2*H115^2+$F$3*H115+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="H116">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I116">
+        <f>IF(H116="","",$F$1*H116^3+$F$2*H116^2+$F$3*H116+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="H117">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I117">
+        <f>IF(H117="","",$F$1*H117^3+$F$2*H117^2+$F$3*H117+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="H118">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I118">
+        <f>IF(H118="","",$F$1*H118^3+$F$2*H118^2+$F$3*H118+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="H119">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I119">
+        <f>IF(H119="","",$F$1*H119^3+$F$2*H119^2+$F$3*H119+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="H120">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I120">
+        <f>IF(H120="","",$F$1*H120^3+$F$2*H120^2+$F$3*H120+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="H121">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I121">
+        <f>IF(H121="","",$F$1*H121^3+$F$2*H121^2+$F$3*H121+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="H122">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I122">
+        <f>IF(H122="","",$F$1*H122^3+$F$2*H122^2+$F$3*H122+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="H123">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I123">
+        <f>IF(H123="","",$F$1*H123^3+$F$2*H123^2+$F$3*H123+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="H124">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I124">
+        <f>IF(H124="","",$F$1*H124^3+$F$2*H124^2+$F$3*H124+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="H125">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I125">
+        <f>IF(H125="","",$F$1*H125^3+$F$2*H125^2+$F$3*H125+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="H126">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I126">
+        <f>IF(H126="","",$F$1*H126^3+$F$2*H126^2+$F$3*H126+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="H127">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I127">
+        <f>IF(H127="","",$F$1*H127^3+$F$2*H127^2+$F$3*H127+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="H128">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I128">
+        <f>IF(H128="","",$F$1*H128^3+$F$2*H128^2+$F$3*H128+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="H129">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I129">
+        <f>IF(H129="","",$F$1*H129^3+$F$2*H129^2+$F$3*H129+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="H130">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I130">
+        <f>IF(H130="","",$F$1*H130^3+$F$2*H130^2+$F$3*H130+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="H131">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I131">
+        <f>IF(H131="","",$F$1*H131^3+$F$2*H131^2+$F$3*H131+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="H132">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I132">
+        <f>IF(H132="","",$F$1*H132^3+$F$2*H132^2+$F$3*H132+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="H133">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I133">
+        <f>IF(H133="","",$F$1*H133^3+$F$2*H133^2+$F$3*H133+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="H134">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I134">
+        <f>IF(H134="","",$F$1*H134^3+$F$2*H134^2+$F$3*H134+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="H135">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I135">
+        <f>IF(H135="","",$F$1*H135^3+$F$2*H135^2+$F$3*H135+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="H136">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I136">
+        <f>IF(H136="","",$F$1*H136^3+$F$2*H136^2+$F$3*H136+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="H137">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I137">
+        <f>IF(H137="","",$F$1*H137^3+$F$2*H137^2+$F$3*H137+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="H138">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I138">
+        <f>IF(H138="","",$F$1*H138^3+$F$2*H138^2+$F$3*H138+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="H139">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I139">
+        <f>IF(H139="","",$F$1*H139^3+$F$2*H139^2+$F$3*H139+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="H140">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I140">
+        <f>IF(H140="","",$F$1*H140^3+$F$2*H140^2+$F$3*H140+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="H141">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I141">
+        <f>IF(H141="","",$F$1*H141^3+$F$2*H141^2+$F$3*H141+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="H142">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I142">
+        <f>IF(H142="","",$F$1*H142^3+$F$2*H142^2+$F$3*H142+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="H143">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I143">
+        <f>IF(H143="","",$F$1*H143^3+$F$2*H143^2+$F$3*H143+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="H144">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I144">
+        <f>IF(H144="","",$F$1*H144^3+$F$2*H144^2+$F$3*H144+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="H145">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I145">
+        <f>IF(H145="","",$F$1*H145^3+$F$2*H145^2+$F$3*H145+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="H146">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I146">
+        <f>IF(H146="","",$F$1*H146^3+$F$2*H146^2+$F$3*H146+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="H147">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I147">
+        <f>IF(H147="","",$F$1*H147^3+$F$2*H147^2+$F$3*H147+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="H148">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I148">
+        <f>IF(H148="","",$F$1*H148^3+$F$2*H148^2+$F$3*H148+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="H149">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I149">
+        <f>IF(H149="","",$F$1*H149^3+$F$2*H149^2+$F$3*H149+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="H150">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I150">
+        <f>IF(H150="","",$F$1*H150^3+$F$2*H150^2+$F$3*H150+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="H151">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I151">
+        <f>IF(H151="","",$F$1*H151^3+$F$2*H151^2+$F$3*H151+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="H152">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I152">
+        <f>IF(H152="","",$F$1*H152^3+$F$2*H152^2+$F$3*H152+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="H153">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I153">
+        <f>IF(H153="","",$F$1*H153^3+$F$2*H153^2+$F$3*H153+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="H154">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I154">
+        <f>IF(H154="","",$F$1*H154^3+$F$2*H154^2+$F$3*H154+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="H155">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I155">
+        <f>IF(H155="","",$F$1*H155^3+$F$2*H155^2+$F$3*H155+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="H156">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I156">
+        <f>IF(H156="","",$F$1*H156^3+$F$2*H156^2+$F$3*H156+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="H157">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I157">
+        <f>IF(H157="","",$F$1*H157^3+$F$2*H157^2+$F$3*H157+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="H158">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I158">
+        <f>IF(H158="","",$F$1*H158^3+$F$2*H158^2+$F$3*H158+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="H159">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I159">
+        <f>IF(H159="","",$F$1*H159^3+$F$2*H159^2+$F$3*H159+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="H160">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I160">
+        <f>IF(H160="","",$F$1*H160^3+$F$2*H160^2+$F$3*H160+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="H161">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I161">
+        <f>IF(H161="","",$F$1*H161^3+$F$2*H161^2+$F$3*H161+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="H162">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I162">
+        <f>IF(H162="","",$F$1*H162^3+$F$2*H162^2+$F$3*H162+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="H163">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I163">
+        <f>IF(H163="","",$F$1*H163^3+$F$2*H163^2+$F$3*H163+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="H164">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I164">
+        <f>IF(H164="","",$F$1*H164^3+$F$2*H164^2+$F$3*H164+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="H165">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I165">
+        <f>IF(H165="","",$F$1*H165^3+$F$2*H165^2+$F$3*H165+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="H166">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I166">
+        <f>IF(H166="","",$F$1*H166^3+$F$2*H166^2+$F$3*H166+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="H167">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I167">
+        <f>IF(H167="","",$F$1*H167^3+$F$2*H167^2+$F$3*H167+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="H168">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I168">
+        <f>IF(H168="","",$F$1*H168^3+$F$2*H168^2+$F$3*H168+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="H169">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I169">
+        <f>IF(H169="","",$F$1*H169^3+$F$2*H169^2+$F$3*H169+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="H170">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I170">
+        <f>IF(H170="","",$F$1*H170^3+$F$2*H170^2+$F$3*H170+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="H171">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I171">
+        <f>IF(H171="","",$F$1*H171^3+$F$2*H171^2+$F$3*H171+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="H172">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I172">
+        <f>IF(H172="","",$F$1*H172^3+$F$2*H172^2+$F$3*H172+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="H173">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I173">
+        <f>IF(H173="","",$F$1*H173^3+$F$2*H173^2+$F$3*H173+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="H174">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I174">
+        <f>IF(H174="","",$F$1*H174^3+$F$2*H174^2+$F$3*H174+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="H175">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I175">
+        <f>IF(H175="","",$F$1*H175^3+$F$2*H175^2+$F$3*H175+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="H176">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I176">
+        <f>IF(H176="","",$F$1*H176^3+$F$2*H176^2+$F$3*H176+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="H177">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I177">
+        <f>IF(H177="","",$F$1*H177^3+$F$2*H177^2+$F$3*H177+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="H178">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I178">
+        <f>IF(H178="","",$F$1*H178^3+$F$2*H178^2+$F$3*H178+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="H179">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I179">
+        <f>IF(H179="","",$F$1*H179^3+$F$2*H179^2+$F$3*H179+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="H180">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I180">
+        <f>IF(H180="","",$F$1*H180^3+$F$2*H180^2+$F$3*H180+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="H181">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I181">
+        <f>IF(H181="","",$F$1*H181^3+$F$2*H181^2+$F$3*H181+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="H182">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I182">
+        <f>IF(H182="","",$F$1*H182^3+$F$2*H182^2+$F$3*H182+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="H183">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I183">
+        <f>IF(H183="","",$F$1*H183^3+$F$2*H183^2+$F$3*H183+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="H184">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I184">
+        <f>IF(H184="","",$F$1*H184^3+$F$2*H184^2+$F$3*H184+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="H185">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I185">
+        <f>IF(H185="","",$F$1*H185^3+$F$2*H185^2+$F$3*H185+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="H186">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I186">
+        <f>IF(H186="","",$F$1*H186^3+$F$2*H186^2+$F$3*H186+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="H187">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I187">
+        <f>IF(H187="","",$F$1*H187^3+$F$2*H187^2+$F$3*H187+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="H188">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I188">
+        <f>IF(H188="","",$F$1*H188^3+$F$2*H188^2+$F$3*H188+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="H189">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I189">
+        <f>IF(H189="","",$F$1*H189^3+$F$2*H189^2+$F$3*H189+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="H190">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I190">
+        <f>IF(H190="","",$F$1*H190^3+$F$2*H190^2+$F$3*H190+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="H191">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I191">
+        <f>IF(H191="","",$F$1*H191^3+$F$2*H191^2+$F$3*H191+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="H192">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I192">
+        <f>IF(H192="","",$F$1*H192^3+$F$2*H192^2+$F$3*H192+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="H193">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I193">
+        <f>IF(H193="","",$F$1*H193^3+$F$2*H193^2+$F$3*H193+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="H194">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I194">
+        <f>IF(H194="","",$F$1*H194^3+$F$2*H194^2+$F$3*H194+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="H195">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I195">
+        <f>IF(H195="","",$F$1*H195^3+$F$2*H195^2+$F$3*H195+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="H196">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I196">
+        <f>IF(H196="","",$F$1*H196^3+$F$2*H196^2+$F$3*H196+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="H197">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I197">
+        <f>IF(H197="","",$F$1*H197^3+$F$2*H197^2+$F$3*H197+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="H198">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I198">
+        <f>IF(H198="","",$F$1*H198^3+$F$2*H198^2+$F$3*H198+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="H199">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I199">
+        <f>IF(H199="","",$F$1*H199^3+$F$2*H199^2+$F$3*H199+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="H200">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I200">
+        <f>IF(H200="","",$F$1*H200^3+$F$2*H200^2+$F$3*H200+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="H201">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I201">
+        <f>IF(H201="","",$F$1*H201^3+$F$2*H201^2+$F$3*H201+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="H202">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I202">
+        <f>IF(H202="","",$F$1*H202^3+$F$2*H202^2+$F$3*H202+$G$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="H203">
+        <f>IF(OR(COUNT($A$3:$A$6)&lt;4,NOT(ISNUMBER($G$2))),"",$G$2+(ROW()-3)*$G$3)</f>
+        <v/>
+      </c>
+      <c r="I203">
+        <f>IF(H203="","",$F$1*H203^3+$F$2*H203^2+$F$3*H203+$G$1)</f>
         <v/>
       </c>
     </row>
@@ -2199,7 +4041,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Ajuste Cuadrático</t>
+          <t>Ajuste MTC (Cúbico)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -2209,12 +4051,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>'_DATOS'!$H$3:$H$22</t>
+          <t>'_DATOS'!$H$3:$H$203</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>'_DATOS'!$I$3:$I$22</t>
+          <t>'_DATOS'!$I$3:$I$203</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
